--- a/hospital/потолок/поликлиника потолок.xlsx
+++ b/hospital/потолок/поликлиника потолок.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Ед. изм.</t>
   </si>
@@ -43,13 +43,16 @@
     <t>Итог:</t>
   </si>
   <si>
-    <t>1-5 этаж</t>
-  </si>
-  <si>
     <t>№ эт.</t>
   </si>
   <si>
     <t>Шлифование бетонных поверхностей потолка (снятие наплывов и швов, снятие цементного молочка)</t>
+  </si>
+  <si>
+    <t>подвал, 1, 2, 3, 4, 5 этаж</t>
+  </si>
+  <si>
+    <t>подвал</t>
   </si>
 </sst>
 </file>
@@ -57,7 +60,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -176,22 +179,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -202,9 +199,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -221,6 +221,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -528,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
@@ -552,144 +564,157 @@
       <c r="G1" s="8"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="5" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
+        <f>B12</f>
+        <v>8032.0000000000009</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="13"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="6">
+        <v>1389.3</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <v>1</v>
       </c>
-      <c r="G3" s="3">
-        <f>B11</f>
-        <v>6642.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-    </row>
-    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="3">
+      <c r="B7" s="2">
         <v>1375.5</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-    </row>
-    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+      <c r="C7" s="13"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <v>2</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B8" s="2">
         <v>1419.8</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-    </row>
-    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
         <v>3</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B9" s="2">
         <v>1398.1</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-    </row>
-    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
+      <c r="C9" s="13"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
         <v>4</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B10" s="2">
         <v>1400.5</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-    </row>
-    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
+      <c r="C10" s="13"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
         <v>5</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B11" s="2">
         <v>1048.8</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-    </row>
-    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="C11" s="13"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+    </row>
+    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="3">
-        <f>SUM(B6:B10)</f>
-        <v>6642.7</v>
-      </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
+      <c r="B12" s="2">
+        <f>SUM(B6:B11)</f>
+        <v>8032.0000000000009</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -697,7 +722,7 @@
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="C5:G11"/>
+    <mergeCell ref="C5:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
